--- a/Result/profitability/5302.xlsx
+++ b/Result/profitability/5302.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.19</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.06125000000000001</v>
+        <v>-0.0575</v>
       </c>
       <c r="N2" t="n">
-        <v>27.655</v>
+        <v>26.33875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.21</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.07875</v>
+        <v>-0.07375</v>
       </c>
       <c r="N3" t="n">
-        <v>23.87875</v>
+        <v>26.19875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.15</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.08750000000000001</v>
+        <v>-0.08125</v>
       </c>
       <c r="N4" t="n">
-        <v>23.9175</v>
+        <v>27.9775</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.24</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.23125</v>
+        <v>-0.22625</v>
       </c>
       <c r="N5" t="n">
-        <v>25.2775</v>
+        <v>24.53625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.33</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2625</v>
+        <v>-0.265</v>
       </c>
       <c r="N6" t="n">
-        <v>23.21375</v>
+        <v>22.65375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.01</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.25875</v>
+        <v>-0.27375</v>
       </c>
       <c r="N7" t="n">
-        <v>22.5275</v>
+        <v>23.49625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,10 +1276,10 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1394,7 +1394,7 @@
         <v>-0.29</v>
       </c>
       <c r="N8" t="n">
-        <v>22.07625</v>
+        <v>23.29875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" t="n">
+        <v>36.03</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-152.74%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.0425</v>
+      </c>
+      <c r="N75" t="n">
+        <v>30.07625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>9.780000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3725714285714286</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.93</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1413250714966635</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
